--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487078_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487078_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.995</v>
+        <v>4.9429</v>
       </c>
       <c r="E2" t="n">
-        <v>1.571</v>
+        <v>2.3315</v>
       </c>
       <c r="F2" t="n">
-        <v>2.424</v>
+        <v>2.6114</v>
       </c>
       <c r="G2" t="n">
         <v>5.8636</v>
@@ -610,13 +610,13 @@
         <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.9764</v>
+        <v>-2.0286</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2347</v>
+        <v>-0.4742</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.7418</v>
+        <v>-1.5544</v>
       </c>
       <c r="V2" t="n">
         <v>0.7219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4293</v>
+        <v>3.4353</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6388</v>
+        <v>3.6983</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2095</v>
+        <v>-0.2631</v>
       </c>
       <c r="G3" t="n">
         <v>3.2359</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5248</v>
+        <v>-0.5189</v>
       </c>
       <c r="T3" t="n">
-        <v>0.279</v>
+        <v>0.3385</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8038</v>
+        <v>-0.8573</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6328</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0613</v>
+        <v>2.9879</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6409</v>
+        <v>3.5408</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5797</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>1.3541</v>
@@ -766,13 +766,13 @@
         <v>2.8951</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4509</v>
+        <v>-1.5243</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3834</v>
+        <v>0.2833</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.8343</v>
+        <v>-1.8075</v>
       </c>
       <c r="V4" t="n">
         <v>1.228</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2142</v>
+        <v>0.7951</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4649</v>
+        <v>0.5453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7493</v>
+        <v>0.2498</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1488</v>
+        <v>0.6503</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0363</v>
+        <v>0.6096</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8875</v>
+        <v>0.0407</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2915</v>
+        <v>0.7238</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1859</v>
+        <v>0.6831</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1057</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4403</v>
+        <v>-0.0735</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2222</v>
+        <v>-0.0735</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7818000000000001</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5091</v>
+        <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4205</v>
+        <v>-0.1484</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5197</v>
+        <v>-0.1785</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0993</v>
+        <v>0.0301</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2936</v>
+        <v>-0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2202</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>J. UGARTE JAUREGUI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8754</v>
+        <v>0.1748</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5453</v>
+        <v>0.9957</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3301</v>
+        <v>-0.8209</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6503</v>
+        <v>0.8863</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6096</v>
+        <v>0.5507</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0407</v>
+        <v>0.3356</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7238</v>
+        <v>1.4268</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6831</v>
+        <v>1.3454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>0.0814</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0735</v>
+        <v>-0.5406</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0735</v>
+        <v>-0.7948</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.2542</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-1.2132</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1785</v>
+        <v>0.2251</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1104</v>
+        <v>-1.4383</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2859</v>
+        <v>-0.6562</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>J. SANCHEZ MARROYO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6937</v>
+        <v>0.1393</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7876</v>
+        <v>-0.0388</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0939</v>
+        <v>0.1781</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7509</v>
+        <v>0.1542</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3746</v>
+        <v>0.1542</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3763</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8309</v>
+        <v>0.0207</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3764</v>
+        <v>0.0207</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5455</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08</v>
+        <v>0.1335</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0018</v>
+        <v>0.1335</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9218</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3511</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6768999999999999</v>
+        <v>-0.0149</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6359</v>
+        <v>-0.0595</v>
       </c>
       <c r="U7" t="n">
-        <v>0.041</v>
+        <v>0.0446</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1201</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SANCHEZ MARROYO</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1126</v>
+        <v>-0.0608</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0388</v>
+        <v>0.0866</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1514</v>
+        <v>-0.1475</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1542</v>
+        <v>0.7509</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1542</v>
+        <v>0.3746</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.3763</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0207</v>
+        <v>0.8309</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0207</v>
+        <v>1.3764</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.5455</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1335</v>
+        <v>-0.08</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1335</v>
+        <v>-1.0018</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.9218</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0416</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0595</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0178</v>
+        <v>-0.0126</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.1201</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.406</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. UGARTE JAUREGUI</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5261</v>
+        <v>-0.2472</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2947</v>
+        <v>-1.2374</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8209</v>
+        <v>0.9902</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8863</v>
+        <v>-0.1488</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5507</v>
+        <v>-1.0363</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3356</v>
+        <v>0.8875</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4268</v>
+        <v>0.2915</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3454</v>
+        <v>0.1859</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0814</v>
+        <v>0.1057</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5406</v>
+        <v>-0.4403</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7948</v>
+        <v>-1.2222</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2542</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>1.158</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R9" t="n">
-        <v>1.158</v>
+        <v>2.5091</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9142</v>
+        <v>-0.041</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4759</v>
+        <v>0.8173</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4383</v>
+        <v>-0.8583</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6562</v>
+        <v>1.2936</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6562</v>
+        <v>1.5138</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2202</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2023</v>
+        <v>-1.3768</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0386</v>
+        <v>-1.0793</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1637</v>
+        <v>-0.2976</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6183</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7119</v>
+        <v>-0.8864</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2512</v>
+        <v>0.2105</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9631</v>
+        <v>-1.0969</v>
       </c>
       <c r="V10" t="n">
         <v>1.5138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.015</v>
+        <v>-1.5747</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0883</v>
+        <v>-2.7284</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0733</v>
+        <v>1.1536</v>
       </c>
       <c r="G11" t="n">
         <v>-1.041</v>
@@ -1312,13 +1312,13 @@
         <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8461</v>
+        <v>-1.4059</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5949</v>
+        <v>-0.235</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2513</v>
+        <v>-1.171</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2859</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6102</v>
+        <v>-4.8903</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4832</v>
+        <v>-4.5224</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.127</v>
+        <v>-0.3679</v>
       </c>
       <c r="G12" t="n">
         <v>1.3263</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.242</v>
+        <v>-0.5222</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8778</v>
+        <v>0.083</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3643</v>
+        <v>-0.6052</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4482</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0279</v>
+        <v>4.3255</v>
       </c>
       <c r="E13" t="n">
-        <v>1.294299999999998</v>
+        <v>1.5919</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7334</v>
+        <v>2.7332</v>
       </c>
       <c r="G13" t="n">
         <v>11.4135</v>
@@ -1456,7 +1456,7 @@
         <v>-8.749599999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>9.2179</v>
+        <v>9.217899999999998</v>
       </c>
       <c r="P13" t="n">
         <v>0.9649000000000001</v>
@@ -1468,22 +1468,22 @@
         <v>18.3357</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.678599999999999</v>
+        <v>-8.381500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6479</v>
+        <v>0.9453999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.327</v>
+        <v>-9.326799999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3282000000000005</v>
+        <v>0.3282</v>
       </c>
       <c r="W13" t="n">
         <v>7.0721</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.744</v>
+        <v>-6.743999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3752</v>
+        <v>4.7782</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6691</v>
+        <v>4.6705</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2938</v>
+        <v>0.1077</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4402</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.269</v>
+        <v>1.1339</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2049</v>
+        <v>1.2063</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4739</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>2.5404</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5192</v>
+        <v>1.095</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3101</v>
+        <v>0.415</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7909</v>
+        <v>0.68</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4061</v>
+        <v>-1.3981</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4617</v>
+        <v>-0.1315</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8679</v>
+        <v>-1.2667</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7164</v>
+        <v>-0.871</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4903</v>
+        <v>0.3828</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.774</v>
+        <v>-1.2538</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1225</v>
+        <v>-0.5272</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0286</v>
+        <v>-0.5143</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0939</v>
+        <v>-0.0129</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0677</v>
+        <v>1.0649</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9943</v>
+        <v>1.286</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0733</v>
+        <v>-0.2211</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2436</v>
+        <v>0.6562</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5295</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1822</v>
+        <v>1.0011</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3149</v>
+        <v>1.0784</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8673999999999999</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3981</v>
+        <v>2.585</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1315</v>
+        <v>0.5743</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2667</v>
+        <v>2.0107</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.871</v>
+        <v>3.5729</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3828</v>
+        <v>1.6764</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2538</v>
+        <v>1.8964</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5272</v>
+        <v>-0.9878</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5143</v>
+        <v>-1.1021</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0129</v>
+        <v>0.1142</v>
       </c>
       <c r="P16" t="n">
-        <v>0.772</v>
+        <v>-0.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1521</v>
+        <v>0.2231</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1858</v>
+        <v>0.4429</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0337</v>
+        <v>-0.2198</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6562</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7726</v>
+        <v>0.7664</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3624</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.135</v>
+        <v>1.4291</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2012</v>
@@ -1780,13 +1780,13 @@
         <v>1.7371</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2247</v>
+        <v>0.2185</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2208</v>
+        <v>-0.0796</v>
       </c>
       <c r="U17" t="n">
-        <v>0.004</v>
+        <v>0.2981</v>
       </c>
       <c r="V17" t="n">
         <v>0.9421</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.468</v>
+        <v>0.491</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2773</v>
+        <v>1.3087</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1907</v>
+        <v>-0.8177</v>
       </c>
       <c r="G18" t="n">
-        <v>2.585</v>
+        <v>-1.4061</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5743</v>
+        <v>0.4617</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0107</v>
+        <v>-1.8679</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5729</v>
+        <v>0.7164</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6764</v>
+        <v>1.4903</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8964</v>
+        <v>-0.774</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9878</v>
+        <v>-2.1225</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1021</v>
+        <v>-1.0286</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1142</v>
+        <v>-1.0939</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.579</v>
+        <v>-0.386</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.31</v>
+        <v>2.0395</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3582</v>
+        <v>1.9929</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0482</v>
+        <v>0.0466</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.228</v>
+        <v>0.2436</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0422</v>
+        <v>0.5295</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1857</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>L. DIEZ TIDALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1125</v>
+        <v>-0.4701</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7079</v>
+        <v>-0.4535</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5954</v>
+        <v>-0.0165</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4462</v>
+        <v>-0.9565</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7247</v>
+        <v>-0.6831</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2785</v>
+        <v>-0.2735</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3331</v>
+        <v>-0.3157</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3573</v>
+        <v>-0.3157</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0243</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1132</v>
+        <v>-0.6408</v>
       </c>
       <c r="N19" t="n">
         <v>-0.3674</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2542</v>
+        <v>-0.2735</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3161</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5733</v>
+        <v>0.2935</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5297</v>
+        <v>-0.1378</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0436</v>
+        <v>0.4313</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6985</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3714</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.0699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. DIEZ TIDALA</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4364</v>
+        <v>-1.1569</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5537</v>
+        <v>-0.6202</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1173</v>
+        <v>-0.5367</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9565</v>
+        <v>-1.2266</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6831</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2735</v>
+        <v>-0.2392</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3157</v>
+        <v>-0.8598</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3157</v>
+        <v>-0.9005</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6408</v>
+        <v>-0.3668</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3674</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2735</v>
+        <v>-0.2799</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>-0.193</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3272</v>
+        <v>0.8345</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.238</v>
+        <v>1.2047</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5651</v>
+        <v>-0.3702</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>P. ALBISU ASTIGARRAGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0567</v>
+        <v>-1.2356</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5201</v>
+        <v>-2.0661</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5367</v>
+        <v>0.8305</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2266</v>
+        <v>-0.6745</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9874000000000001</v>
+        <v>1.776</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2392</v>
+        <v>-2.4505</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8598</v>
+        <v>-0.1741</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9005</v>
+        <v>2.3906</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0407</v>
+        <v>-2.5647</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3668</v>
+        <v>-0.5004</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.6146</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2799</v>
+        <v>0.1142</v>
       </c>
       <c r="P21" t="n">
         <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R21" t="n">
-        <v>0.772</v>
+        <v>2.7021</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9346</v>
+        <v>0.2036</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3048</v>
+        <v>1.0031</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3702</v>
+        <v>-0.7995</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5717</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. AZKOAGA BENDEJACQ</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6435</v>
+        <v>-1.3483</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4938</v>
+        <v>-2.379</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1496</v>
+        <v>1.0307</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1335</v>
+        <v>-3.9001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.86</v>
+        <v>0.5839</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2735</v>
+        <v>-4.484</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6262</v>
+        <v>-1.7508</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6262</v>
+        <v>2.1734</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-3.9242</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5073</v>
+        <v>-2.1493</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2338</v>
+        <v>-1.5895</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2735</v>
+        <v>-0.5598</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>0.193</v>
+        <v>2.7021</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0238</v>
+        <v>0.857</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4164</v>
+        <v>0.3791</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3926</v>
+        <v>0.4779</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2859</v>
+        <v>-0.0422</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5138</v>
+        <v>-0.0422</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2225</v>
+        <v>-1.3499</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2802</v>
+        <v>0.4061</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0577</v>
+        <v>-1.756</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.9001</v>
+        <v>-0.4462</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5839</v>
+        <v>-0.7247</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.484</v>
+        <v>0.2785</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7508</v>
+        <v>-0.3331</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1734</v>
+        <v>-0.3573</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.9242</v>
+        <v>0.0243</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1493</v>
+        <v>-0.1132</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5895</v>
+        <v>-0.3674</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5598</v>
+        <v>0.2542</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7371</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7021</v>
+        <v>1.5441</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0172</v>
+        <v>2.1109</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5221</v>
+        <v>2.2279</v>
       </c>
       <c r="U23" t="n">
-        <v>0.505</v>
+        <v>-0.117</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.0422</v>
+        <v>-0.6985</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0422</v>
+        <v>2.3714</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. ALBISU ASTIGARRAGA</t>
+          <t>A. AZKOAGA BENDEJACQ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2714</v>
+        <v>-1.4898</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5668</v>
+        <v>-0.3937</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2954</v>
+        <v>-1.0961</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6745</v>
+        <v>-1.1335</v>
       </c>
       <c r="H24" t="n">
-        <v>1.776</v>
+        <v>-0.86</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.4505</v>
+        <v>-0.2735</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1741</v>
+        <v>-0.6262</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3906</v>
+        <v>-0.6262</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.5647</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5004</v>
+        <v>-0.5073</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6146</v>
+        <v>-0.2338</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1142</v>
+        <v>-0.2735</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7021</v>
+        <v>0.193</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8322000000000001</v>
+        <v>0.1299</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5024</v>
+        <v>-0.3163</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3346</v>
+        <v>0.4462</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5717</v>
+        <v>0.2859</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8272</v>
+        <v>-4.4413</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2356</v>
+        <v>-4.0368</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5916</v>
+        <v>-0.4045</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2154</v>
@@ -2404,13 +2404,13 @@
         <v>1.3511</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8514</v>
+        <v>0.2373</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9188</v>
+        <v>0.1177</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0674</v>
+        <v>0.1196</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8842</v>
@@ -2437,25 +2437,25 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.028</v>
+        <v>-3.3602</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7333</v>
+        <v>-2.7334</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2945</v>
+        <v>-0.6268000000000002</v>
       </c>
       <c r="G26" t="n">
         <v>-11.4134</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6674</v>
+        <v>0.6674000000000002</v>
       </c>
       <c r="I26" t="n">
         <v>-12.0812</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4682999999999997</v>
+        <v>-0.4682999999999995</v>
       </c>
       <c r="K26" t="n">
         <v>8.749399999999998</v>
@@ -2473,7 +2473,7 @@
         <v>-2.8634</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.9649000000000001</v>
+        <v>-0.9648999999999996</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.3357</v>
@@ -2482,16 +2482,16 @@
         <v>17.3708</v>
       </c>
       <c r="S26" t="n">
-        <v>8.678799999999999</v>
+        <v>9.346599999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>9.3268</v>
+        <v>9.3269</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6479999999999999</v>
+        <v>0.01969999999999995</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.3280999999999998</v>
+        <v>-0.3280999999999996</v>
       </c>
       <c r="W26" t="n">
         <v>6.7441</v>
